--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task029.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task029.xlsx
@@ -100,13 +100,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="14.85546875" customWidth="true"/>
     <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="4" max="4" width="10.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="9.5703125" customWidth="true"/>
     <col min="6" max="6" width="16.140625" customWidth="true"/>
     <col min="7" max="7" width="20.85546875" customWidth="true"/>
@@ -559,6 +559,50 @@
         <v>5.2722236333366865</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>103</v>
+      </c>
+      <c r="B11" s="0">
+        <v>290</v>
+      </c>
+      <c r="C11" s="0">
+        <v>103</v>
+      </c>
+      <c r="D11" s="0">
+        <v>94.197147751338065</v>
+      </c>
+      <c r="E11" s="0">
+        <v>470.10500000000002</v>
+      </c>
+      <c r="F11" s="0">
+        <v>156.67051440324366</v>
+      </c>
+      <c r="G11" s="0">
+        <v>3460.6073108830346</v>
+      </c>
+      <c r="H11" s="0">
+        <v>-932.95392209912666</v>
+      </c>
+      <c r="I11" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J11" s="0">
+        <v>15.35</v>
+      </c>
+      <c r="K11" s="0">
+        <v>2.5250000000000004</v>
+      </c>
+      <c r="L11" s="0">
+        <v>3.5900000000000003</v>
+      </c>
+      <c r="M11" s="0">
+        <v>300.04401175372618</v>
+      </c>
+      <c r="N11" s="0">
+        <v>5.2722236333366865</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>